--- a/data/trans_orig/IP05A01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP05A01-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59598</t>
+          <t>58717</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79681</t>
+          <t>77674</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63377</t>
+          <t>63440</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82698</t>
+          <t>82964</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>128010</t>
+          <t>129307</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>155092</t>
+          <t>155987</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,7%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50405</t>
+          <t>51339</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69072</t>
+          <t>70379</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56017</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75990</t>
+          <t>75720</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112780</t>
+          <t>111879</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>139156</t>
+          <t>139902</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>48,17%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14948</t>
+          <t>15218</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18581</t>
+          <t>19901</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16222</t>
+          <t>15913</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31552</t>
+          <t>31829</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85327</t>
+          <t>85764</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>106765</t>
+          <t>107122</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99654</t>
+          <t>100178</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>122563</t>
+          <t>123570</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>191625</t>
+          <t>191826</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>223489</t>
+          <t>223473</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70679</t>
+          <t>70876</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>92409</t>
+          <t>92266</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68361</t>
+          <t>67784</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89766</t>
+          <t>90458</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>144885</t>
+          <t>146661</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>176702</t>
+          <t>177888</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,73%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11736</t>
+          <t>11735</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24036</t>
+          <t>24943</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14984</t>
+          <t>14815</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29063</t>
+          <t>28398</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30170</t>
+          <t>30389</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49027</t>
+          <t>48758</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59816</t>
+          <t>59794</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>78144</t>
+          <t>77931</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>69906</t>
+          <t>70210</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>88782</t>
+          <t>89094</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>136639</t>
+          <t>134588</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>161724</t>
+          <t>160731</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,05%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41604</t>
+          <t>40864</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58875</t>
+          <t>58605</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49011</t>
+          <t>48911</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67350</t>
+          <t>67372</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93442</t>
+          <t>94478</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>119524</t>
+          <t>120469</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>42,01%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12883</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24902</t>
+          <t>25076</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19393</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23373</t>
+          <t>23680</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39994</t>
+          <t>39916</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97930</t>
+          <t>97901</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>122808</t>
+          <t>122448</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87788</t>
+          <t>87824</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>110808</t>
+          <t>110646</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>194277</t>
+          <t>193395</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>229432</t>
+          <t>226448</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>54,29%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57272</t>
+          <t>57969</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80216</t>
+          <t>81014</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70102</t>
+          <t>69842</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92139</t>
+          <t>92741</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>132540</t>
+          <t>134016</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>165818</t>
+          <t>167338</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>40,12%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22416</t>
+          <t>21983</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39808</t>
+          <t>39959</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20413</t>
+          <t>20589</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35130</t>
+          <t>36324</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>46454</t>
+          <t>46215</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>69091</t>
+          <t>69314</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>323385</t>
+          <t>323949</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>365850</t>
+          <t>366486</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>342348</t>
+          <t>342035</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>384980</t>
+          <t>384899</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>676747</t>
+          <t>679411</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>738378</t>
+          <t>740120</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,82%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240528</t>
+          <t>240003</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>279749</t>
+          <t>280691</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>263387</t>
+          <t>263559</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>306490</t>
+          <t>305865</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>515998</t>
+          <t>513998</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>573587</t>
+          <t>572135</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63446</t>
+          <t>62918</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89801</t>
+          <t>89690</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60893</t>
+          <t>62989</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>86700</t>
+          <t>86810</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>130631</t>
+          <t>132373</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>167863</t>
+          <t>169208</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>104357</t>
+          <t>104418</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>120171</t>
+          <t>120205</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>113840</t>
+          <t>115036</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>131419</t>
+          <t>132053</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>224529</t>
+          <t>225846</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>247123</t>
+          <t>246972</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,99%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16056</t>
+          <t>15926</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31414</t>
+          <t>29976</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>20672</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37572</t>
+          <t>36727</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40473</t>
+          <t>39951</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62435</t>
+          <t>60666</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>8019</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>677</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6768</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3279</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11519</t>
+          <t>11445</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>140045</t>
+          <t>139701</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>159848</t>
+          <t>160010</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>160669</t>
+          <t>162372</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>182103</t>
+          <t>182205</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>308821</t>
+          <t>306563</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>337052</t>
+          <t>336884</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,31%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40354</t>
+          <t>39576</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59020</t>
+          <t>59463</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35246</t>
+          <t>35233</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55592</t>
+          <t>53535</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>80450</t>
+          <t>80504</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>107646</t>
+          <t>109101</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11592</t>
+          <t>11253</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>13320</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8635</t>
+          <t>8841</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20604</t>
+          <t>21397</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>99007</t>
+          <t>99484</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>116673</t>
+          <t>118255</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>98929</t>
+          <t>99195</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>118879</t>
+          <t>118918</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>204444</t>
+          <t>204604</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>230345</t>
+          <t>230992</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,88%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25787</t>
+          <t>26221</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42983</t>
+          <t>42665</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35984</t>
+          <t>36130</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54912</t>
+          <t>54743</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67683</t>
+          <t>67718</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91641</t>
+          <t>91707</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7578</t>
+          <t>7691</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18836</t>
+          <t>18510</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18353</t>
+          <t>19050</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17432</t>
+          <t>16508</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32985</t>
+          <t>32035</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>107143</t>
+          <t>106217</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>129574</t>
+          <t>130711</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>113957</t>
+          <t>113834</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>138726</t>
+          <t>137153</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>226237</t>
+          <t>229064</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>261951</t>
+          <t>261391</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,54%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53304</t>
+          <t>52493</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74400</t>
+          <t>76145</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50129</t>
+          <t>50805</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72835</t>
+          <t>72730</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>107906</t>
+          <t>109898</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>143243</t>
+          <t>140542</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19633</t>
+          <t>18787</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36085</t>
+          <t>35127</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>14398</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29776</t>
+          <t>28849</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37589</t>
+          <t>37618</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>60969</t>
+          <t>59096</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>469831</t>
+          <t>469710</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>510101</t>
+          <t>510833</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>510562</t>
+          <t>511230</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>551618</t>
+          <t>551502</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>992589</t>
+          <t>987403</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1051560</t>
+          <t>1050925</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,81%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>150928</t>
+          <t>150204</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>188598</t>
+          <t>188563</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>159966</t>
+          <t>160620</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>199485</t>
+          <t>199076</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>322517</t>
+          <t>323916</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>374905</t>
+          <t>378261</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39385</t>
+          <t>38858</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>62589</t>
+          <t>61677</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32848</t>
+          <t>33079</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54253</t>
+          <t>54484</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>77907</t>
+          <t>76671</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>109046</t>
+          <t>108353</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106268</t>
+          <t>106248</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>120455</t>
+          <t>120351</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>116687</t>
+          <t>117590</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>131975</t>
+          <t>132047</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>229840</t>
+          <t>227309</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>249770</t>
+          <t>248457</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,17%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12068</t>
+          <t>12358</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25391</t>
+          <t>25983</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10175</t>
+          <t>9739</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22982</t>
+          <t>22174</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24990</t>
+          <t>25208</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42949</t>
+          <t>44324</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4429</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>15398</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>144588</t>
+          <t>143472</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>163368</t>
+          <t>163284</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>160662</t>
+          <t>161752</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>181228</t>
+          <t>182067</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>310963</t>
+          <t>310146</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>338699</t>
+          <t>339164</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,58%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36063</t>
+          <t>36412</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54105</t>
+          <t>54662</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32179</t>
+          <t>32453</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51120</t>
+          <t>49801</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>73787</t>
+          <t>73229</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>99658</t>
+          <t>101597</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13612</t>
+          <t>12628</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19107</t>
+          <t>17827</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13942</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28045</t>
+          <t>27881</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>90123</t>
+          <t>90199</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>108295</t>
+          <t>108370</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>99713</t>
+          <t>99767</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>119503</t>
+          <t>119430</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>194492</t>
+          <t>194396</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>222446</t>
+          <t>222315</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,9%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38487</t>
+          <t>38892</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55515</t>
+          <t>55848</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39392</t>
+          <t>38246</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57995</t>
+          <t>57728</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81911</t>
+          <t>82682</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>108989</t>
+          <t>109322</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14309</t>
+          <t>15054</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5362</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15656</t>
+          <t>15436</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12668</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25425</t>
+          <t>26472</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>136626</t>
+          <t>136023</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>159440</t>
+          <t>159137</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>123199</t>
+          <t>123583</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145584</t>
+          <t>145896</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>267758</t>
+          <t>267601</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>298751</t>
+          <t>300533</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,95%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29587</t>
+          <t>29348</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48709</t>
+          <t>48853</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47184</t>
+          <t>47435</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68213</t>
+          <t>67822</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81353</t>
+          <t>82222</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>111148</t>
+          <t>110790</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12617</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27538</t>
+          <t>27271</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8397</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>20255</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24618</t>
+          <t>24639</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>43184</t>
+          <t>42936</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>498193</t>
+          <t>497520</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>535248</t>
+          <t>534620</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>520398</t>
+          <t>520794</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>561319</t>
+          <t>561133</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1027975</t>
+          <t>1031424</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1087717</t>
+          <t>1086688</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,05%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>131182</t>
+          <t>131657</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>167669</t>
+          <t>166608</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>142154</t>
+          <t>141837</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>180062</t>
+          <t>179578</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>285007</t>
+          <t>284855</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>337274</t>
+          <t>335323</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29050</t>
+          <t>28752</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49561</t>
+          <t>48538</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31427</t>
+          <t>32370</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52274</t>
+          <t>53606</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66719</t>
+          <t>67791</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95610</t>
+          <t>95949</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98591</t>
+          <t>98365</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110062</t>
+          <t>110210</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>125077</t>
+          <t>124315</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>136433</t>
+          <t>136437</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>227681</t>
+          <t>228576</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>244010</t>
+          <t>243894</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,64%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14264</t>
+          <t>15275</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13320</t>
+          <t>13331</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9132</t>
+          <t>9250</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23187</t>
+          <t>22724</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>704</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>7353</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10422</t>
+          <t>10425</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>146879</t>
+          <t>146899</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>165968</t>
+          <t>165211</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>203542</t>
+          <t>205145</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>226328</t>
+          <t>227266</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>356217</t>
+          <t>358312</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>386720</t>
+          <t>387703</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>87,02%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17744</t>
+          <t>18145</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34747</t>
+          <t>34997</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20826</t>
+          <t>19946</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41453</t>
+          <t>41413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>42799</t>
+          <t>41785</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>69362</t>
+          <t>69057</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15149</t>
+          <t>14506</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15737</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11494</t>
+          <t>11540</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26691</t>
+          <t>26213</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77864</t>
+          <t>75319</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>159585</t>
+          <t>159685</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>139438</t>
+          <t>140813</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>162381</t>
+          <t>162972</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>216461</t>
+          <t>213855</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>314451</t>
+          <t>313990</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,58%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>22571</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110567</t>
+          <t>110933</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18542</t>
+          <t>17253</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39543</t>
+          <t>38051</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47479</t>
+          <t>48071</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149355</t>
+          <t>150941</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,18%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12668</t>
+          <t>12645</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11292</t>
+          <t>12424</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21214</t>
+          <t>20399</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>103463</t>
+          <t>104954</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>124048</t>
+          <t>125603</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99248</t>
+          <t>99500</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>122356</t>
+          <t>123345</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>211930</t>
+          <t>213817</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>241246</t>
+          <t>242482</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,91%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33872</t>
+          <t>33009</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53538</t>
+          <t>51740</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34536</t>
+          <t>33778</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56052</t>
+          <t>55126</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>73031</t>
+          <t>73533</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>100529</t>
+          <t>101588</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14337</t>
+          <t>14584</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17666</t>
+          <t>17016</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34257</t>
+          <t>33818</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24748</t>
+          <t>24641</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>45465</t>
+          <t>43849</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>443413</t>
+          <t>443232</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>539362</t>
+          <t>540857</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>591604</t>
+          <t>588423</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>632453</t>
+          <t>633833</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1051606</t>
+          <t>1048628</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1159720</t>
+          <t>1160105</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,37%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>96740</t>
+          <t>95807</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>196632</t>
+          <t>199282</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>88434</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>125982</t>
+          <t>128318</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>197853</t>
+          <t>197631</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>310250</t>
+          <t>311434</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19373</t>
+          <t>19403</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38084</t>
+          <t>37070</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32037</t>
+          <t>31035</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54297</t>
+          <t>55013</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55904</t>
+          <t>56694</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85471</t>
+          <t>85523</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
